--- a/output/2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx
+++ b/output/2026-09-06_08_Slovenia_Zasavska_Depolverazione_Trattamento_aria.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Progettazione, produzione e installazione impianti di odpraševanje (dedusting) industriale, lunga tradizione, sede Ajdovska cesta 2, Bohinjska Bistrica.</t>
+          <t>Progettazione, produzione e installazione impianti di odpraševanje (dedusting) industriale, lunga tradizione, sede Ajdovska cesta 2, Bohinjska Bistrica. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -527,7 +527,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vendita sistemi/impianti per odpraševanje industriale (polveri, fumi, nebbie oleose), progetti chiavi in mano. Sede Ptuj.</t>
+          <t>Vendita sistemi/impianti per odpraševanje industriale (polveri, fumi, nebbie oleose), progetti chiavi in mano. Sede Ptuj. [DUPLICATO — vedi anche: 2026-09-05_23_Slovenia_Podravska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -564,7 +564,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ventilazione, filtrazione industriale, impianti HVAC industriali. Sede Domžale.</t>
+          <t>Ventilazione, filtrazione industriale, impianti HVAC industriali. Sede Domžale. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>35+ anni attivita, sviluppo/produzione/installazione sistemi filtranti per fonderie, cementifici, cave. Sede reale: Dobja vas 191, Ravne na Koroškem.</t>
+          <t>35+ anni attivita, sviluppo/produzione/installazione sistemi filtranti per fonderie, cementifici, cave. Sede reale: Dobja vas 191, Ravne na Koroškem. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ingegneria, produzione, vendita e assistenza sistemi di filtrazione aria/liquidi. Sede Slovenske Konjice. Non duplicato di Ecotip.</t>
+          <t>Ingegneria, produzione, vendita e assistenza sistemi di filtrazione aria/liquidi. Sede Slovenske Konjice. Non duplicato di Ecotip. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Produttore marchio filtri ECOFIL (aria e liquidi), fondata 1993, 90+ dipendenti, esporta in 24 paesi. Sede Slovenske Konjice.</t>
+          <t>Produttore marchio filtri ECOFIL (aria e liquidi), fondata 1993, 90+ dipendenti, esporta in 24 paesi. Sede Slovenske Konjice. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Progettazione/produzione impianti di sabbiatura e odpraševanje industriale per fonderie terze, dal 1996. Sede Ajdovščina.</t>
+          <t>Progettazione/produzione impianti di sabbiatura e odpraševanje industriale per fonderie terze, dal 1996. Sede Ajdovščina. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rappresentante ufficiale Nederman (Svezia) per aspirazione/depolverazione industriale e Lincoln Electric per saldatura. Sede Ljubljana-Črnuče.</t>
+          <t>Rappresentante ufficiale Nederman (Svezia) per aspirazione/depolverazione industriale e Lincoln Electric per saldatura. Sede Ljubljana-Črnuče. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fornitura, progettazione e importazione aspiratori industriali e sistemi centralizzati di aspirazione. Sede Celje.</t>
+          <t>Fornitura, progettazione e importazione aspiratori industriali e sistemi centralizzati di aspirazione. Sede Celje. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vendita cabine di sabbiatura/verniciatura con unità filtranti per depolverazione, compressori, noleggio. Nota: alcune fonti indicano anche servizio di sabbiatura conto terzi. Sede Bizeljsko.</t>
+          <t>Vendita cabine di sabbiatura/verniciatura con unità filtranti per depolverazione, compressori, noleggio. Nota: alcune fonti indicano anche servizio di sabbiatura conto terzi. Sede Bizeljsko. [DUPLICATO — vedi anche: 2026-09-06_05_Slovenia_Savinjska_Depolverazione_Trattamento_aria.xlsx]</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rivenditore tecnico generalista con sezione B2B dedicata e ampia gamma di aspiratori industriali (vendita e noleggio). Sede Celje, filiali in tutta la Slovenia.</t>
+          <t>Rivenditore tecnico generalista con sezione B2B dedicata e ampia gamma di aspiratori industriali (vendita e noleggio). Sede Celje, filiali in tutta la Slovenia. [DUPLICATO — vedi anche: 2026-09-06_03_Slovenia_Koroska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1045,7 +1045,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rivenditore FESTOOL/FEIN, gamma aspiratori industriali (classe L). Distributore generalista di utensili. Sede reale: Žolgarjeva ulica 27, Slovenska Bistrica.</t>
+          <t>Rivenditore FESTOOL/FEIN, gamma aspiratori industriali (classe L). Distributore generalista di utensili. Sede reale: Žolgarjeva ulica 27, Slovenska Bistrica. [DUPLICATO — vedi anche: 2026-09-06_01_Slovenia_Podravska_Metalworking_Lavorazioni_Metalliche.xlsx]</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1119,7 +1119,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Negozio fisico e online di aspiratori industriali per officina/cantiere (Lavor, Makita ecc.). Distributore generalista. Sede Celje.</t>
+          <t>Negozio fisico e online di aspiratori industriali per officina/cantiere (Lavor, Makita ecc.). Distributore generalista. Sede Celje. [DUPLICATO — vedi anche: 2026-09-06_06_Slovenia_Savinjska_Utensilerie_e_Macchine_Utensili.xlsx]</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
